--- a/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/region-de-valparaiso.xlsx
+++ b/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/region-de-valparaiso.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>544143-9-CM26</t>
+          <t>544143-1-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -569,6 +569,803 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
+        <v>30183.07</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>544143-2-CM25</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>feb-2025</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>31876.29</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>544143-3-CM25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>33074.59</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>544143-6-CM25</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>32668.39</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>544143-7-CM25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>33001.67</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3134-187-CM25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>61.102.014-7</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>58799.48</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>544143-9-CM25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>32929.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3134-257-CM25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>61.102.014-7</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>29274.59</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3134-260-CM25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>61.102.014-7</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>67597.69</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>544143-10-CM25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>31494.61</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>5212-13-CM25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>60.921.000-1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Tarapacá  </t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>923764.08</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>544143-12-CM25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>31911.74</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>544143-13-CM25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>32699.85</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>544143-9-CM26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
         <v>37448.52</v>
       </c>
     </row>
